--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_8F3D3109B6CE6C95635AAC206AEC06CC75D307F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ABA9C90-2653-452D-8790-4C7FF88EFC3D}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_8F3D3109B6CE6C95635AAC206AEC06CC75D307F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B774F01-CEE9-4A8E-AA43-44D82AF7B7DA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="766">
   <si>
     <t>S.no</t>
   </si>
@@ -2339,6 +2339,9 @@
   </si>
   <si>
     <t>For the Month of XXXX - 20XX</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -2899,7 +2902,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3507,6 +3510,18 @@
       <alignment wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -3517,23 +3532,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="centerContinuous"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -3870,7 +3870,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:CV172"/>
+  <dimension ref="A1:CS172"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.77734375" style="16" bestFit="1" customWidth="1"/>
@@ -3973,7 +3973,7 @@
     <col min="99" max="16384" width="8.88671875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:94" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="32"/>
       <c r="B1" s="32" t="s">
         <v>764</v>
@@ -4055,7 +4055,7 @@
       <c r="BY1" s="120"/>
       <c r="BZ1" s="120"/>
     </row>
-    <row r="2" spans="1:100" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:94" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
       <c r="B2" s="32" t="s">
         <v>629</v>
@@ -4137,169 +4137,171 @@
       <c r="BY2" s="120"/>
       <c r="BZ2" s="120"/>
     </row>
-    <row r="3" spans="1:100" x14ac:dyDescent="0.3">
-      <c r="B3" s="150"/>
-      <c r="C3" s="150"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
+    <row r="3" spans="1:94" x14ac:dyDescent="0.3">
+      <c r="B3" s="177" t="s">
+        <v>765</v>
+      </c>
+      <c r="C3" s="177"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="150"/>
       <c r="H3" s="119"/>
       <c r="I3" s="119"/>
-      <c r="J3" s="175">
+      <c r="J3" s="31">
         <v>1</v>
       </c>
-      <c r="K3" s="175"/>
-      <c r="L3" s="175">
+      <c r="K3" s="31"/>
+      <c r="L3" s="31">
         <f>+J3+1</f>
         <v>2</v>
       </c>
-      <c r="M3" s="175"/>
-      <c r="N3" s="175">
+      <c r="M3" s="31"/>
+      <c r="N3" s="31">
         <f>+L3+1</f>
         <v>3</v>
       </c>
-      <c r="O3" s="175"/>
-      <c r="P3" s="175">
+      <c r="O3" s="31"/>
+      <c r="P3" s="31">
         <f>+N3+1</f>
         <v>4</v>
       </c>
-      <c r="Q3" s="175"/>
-      <c r="R3" s="175">
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31">
         <f>+P3+1</f>
         <v>5</v>
       </c>
-      <c r="S3" s="175"/>
-      <c r="T3" s="175">
+      <c r="S3" s="31"/>
+      <c r="T3" s="31">
         <f>+R3+1</f>
         <v>6</v>
       </c>
-      <c r="U3" s="175"/>
-      <c r="V3" s="175">
+      <c r="U3" s="31"/>
+      <c r="V3" s="31">
         <f>+T3+1</f>
         <v>7</v>
       </c>
-      <c r="W3" s="175"/>
-      <c r="X3" s="175">
+      <c r="W3" s="31"/>
+      <c r="X3" s="31">
         <f>+V3+1</f>
         <v>8</v>
       </c>
-      <c r="Y3" s="175"/>
-      <c r="Z3" s="175">
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31">
         <f>+X3+1</f>
         <v>9</v>
       </c>
-      <c r="AA3" s="175"/>
-      <c r="AB3" s="175">
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31">
         <f>+Z3+1</f>
         <v>10</v>
       </c>
-      <c r="AC3" s="175"/>
-      <c r="AD3" s="175">
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31">
         <f>+AB3+1</f>
         <v>11</v>
       </c>
-      <c r="AE3" s="175"/>
-      <c r="AF3" s="175">
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31">
         <f>+AD3+1</f>
         <v>12</v>
       </c>
-      <c r="AG3" s="175"/>
-      <c r="AH3" s="175">
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31">
         <f>+AF3+1</f>
         <v>13</v>
       </c>
-      <c r="AI3" s="175"/>
-      <c r="AJ3" s="175">
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31">
         <f>+AH3+1</f>
         <v>14</v>
       </c>
-      <c r="AK3" s="175"/>
-      <c r="AL3" s="175">
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31">
         <f>+AJ3+1</f>
         <v>15</v>
       </c>
-      <c r="AM3" s="175"/>
-      <c r="AN3" s="175">
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31">
         <f>+AL3+1</f>
         <v>16</v>
       </c>
-      <c r="AO3" s="175"/>
-      <c r="AP3" s="175">
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31">
         <f>+AN3+1</f>
         <v>17</v>
       </c>
-      <c r="AQ3" s="175"/>
-      <c r="AR3" s="175">
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31">
         <f>+AP3+1</f>
         <v>18</v>
       </c>
-      <c r="AS3" s="175"/>
-      <c r="AT3" s="175">
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31">
         <f>+AR3+1</f>
         <v>19</v>
       </c>
-      <c r="AU3" s="175"/>
-      <c r="AV3" s="175">
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31">
         <f>+AT3+1</f>
         <v>20</v>
       </c>
-      <c r="AW3" s="175"/>
-      <c r="AX3" s="175">
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31">
         <f>+AV3+1</f>
         <v>21</v>
       </c>
-      <c r="AY3" s="175"/>
-      <c r="AZ3" s="175">
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31">
         <f>+AX3+1</f>
         <v>22</v>
       </c>
-      <c r="BA3" s="175"/>
-      <c r="BB3" s="175">
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31">
         <f>+AZ3+1</f>
         <v>23</v>
       </c>
-      <c r="BC3" s="175"/>
-      <c r="BD3" s="175">
+      <c r="BC3" s="31"/>
+      <c r="BD3" s="31">
         <f>+BB3+1</f>
         <v>24</v>
       </c>
-      <c r="BE3" s="175"/>
-      <c r="BF3" s="175">
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="31">
         <f>+BD3+1</f>
         <v>25</v>
       </c>
-      <c r="BG3" s="175"/>
-      <c r="BH3" s="175">
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="31">
         <f>+BF3+1</f>
         <v>26</v>
       </c>
-      <c r="BI3" s="175"/>
-      <c r="BJ3" s="175">
+      <c r="BI3" s="31"/>
+      <c r="BJ3" s="31">
         <f>+BH3+1</f>
         <v>27</v>
       </c>
-      <c r="BK3" s="174"/>
-      <c r="BL3" s="175">
+      <c r="BK3" s="171"/>
+      <c r="BL3" s="31">
         <f>+BJ3+1</f>
         <v>28</v>
       </c>
-      <c r="BM3" s="175"/>
-      <c r="BN3" s="175">
+      <c r="BM3" s="31"/>
+      <c r="BN3" s="31">
         <f>+BL3+1</f>
         <v>29</v>
       </c>
-      <c r="BO3" s="175"/>
-      <c r="BP3" s="176">
+      <c r="BO3" s="31"/>
+      <c r="BP3" s="172">
         <f>+BN3+1</f>
         <v>30</v>
       </c>
-      <c r="BQ3" s="177"/>
-      <c r="BR3" s="176">
+      <c r="BQ3" s="173"/>
+      <c r="BR3" s="172">
         <f>+BP3+1</f>
         <v>31</v>
       </c>
-      <c r="BS3" s="177"/>
+      <c r="BS3" s="173"/>
       <c r="CA3" s="148" t="s">
         <v>706</v>
       </c>
@@ -4308,9 +4310,8 @@
       <c r="CD3" s="149"/>
       <c r="CE3" s="149"/>
       <c r="CF3" s="149"/>
-      <c r="CV3" s="178"/>
-    </row>
-    <row r="4" spans="1:100" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:94" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
         <v>0</v>
       </c>
@@ -4589,7 +4590,7 @@
       </c>
       <c r="CP4" s="154"/>
     </row>
-    <row r="5" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A5" s="41">
         <v>1</v>
       </c>
@@ -4767,7 +4768,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:100" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:94" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <f>A5+1</f>
         <v>2</v>
@@ -4942,7 +4943,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <f t="shared" ref="A7:A70" si="7">A6+1</f>
         <v>3</v>
@@ -5121,7 +5122,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -5300,7 +5301,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="9" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A9" s="41">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -5479,7 +5480,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -5658,7 +5659,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:100" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:94" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="41">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -5837,7 +5838,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -6017,7 +6018,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -6195,7 +6196,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:100" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:94" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -6373,7 +6374,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A15" s="41">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -6553,7 +6554,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:100" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <f>A15+1</f>
         <v>12</v>
@@ -33460,16 +33461,16 @@
       <c r="F4" s="66"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="171" t="s">
+      <c r="I4" s="174" t="s">
         <v>498</v>
       </c>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="171" t="s">
+      <c r="J4" s="175"/>
+      <c r="K4" s="175"/>
+      <c r="L4" s="176"/>
+      <c r="M4" s="174" t="s">
         <v>499</v>
       </c>
-      <c r="N4" s="173"/>
+      <c r="N4" s="176"/>
       <c r="O4" s="67"/>
       <c r="BU4" s="169"/>
       <c r="BX4" s="169"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_8F3D3109B6CE6C95635AAC206AEC06CC75D307F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B774F01-CEE9-4A8E-AA43-44D82AF7B7DA}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_8F3D3109B6CE6C95635AAC206AEC06CC75D307F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1672050C-86B0-4078-9FA1-F55EEA91C08A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3514,6 +3514,10 @@
       <alignment horizontal="centerContinuous"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -3530,10 +3534,6 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -3580,6 +3580,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4138,10 +4142,10 @@
       <c r="BZ2" s="120"/>
     </row>
     <row r="3" spans="1:94" x14ac:dyDescent="0.3">
-      <c r="B3" s="177" t="s">
+      <c r="B3" s="172" t="s">
         <v>765</v>
       </c>
-      <c r="C3" s="177"/>
+      <c r="C3" s="172"/>
       <c r="D3" s="31"/>
       <c r="E3" s="31"/>
       <c r="F3" s="31"/>
@@ -4153,155 +4157,125 @@
       </c>
       <c r="K3" s="31"/>
       <c r="L3" s="31">
-        <f>+J3+1</f>
         <v>2</v>
       </c>
       <c r="M3" s="31"/>
       <c r="N3" s="31">
-        <f>+L3+1</f>
         <v>3</v>
       </c>
       <c r="O3" s="31"/>
       <c r="P3" s="31">
-        <f>+N3+1</f>
         <v>4</v>
       </c>
       <c r="Q3" s="31"/>
       <c r="R3" s="31">
-        <f>+P3+1</f>
         <v>5</v>
       </c>
       <c r="S3" s="31"/>
       <c r="T3" s="31">
-        <f>+R3+1</f>
         <v>6</v>
       </c>
       <c r="U3" s="31"/>
       <c r="V3" s="31">
-        <f>+T3+1</f>
         <v>7</v>
       </c>
       <c r="W3" s="31"/>
       <c r="X3" s="31">
-        <f>+V3+1</f>
         <v>8</v>
       </c>
       <c r="Y3" s="31"/>
       <c r="Z3" s="31">
-        <f>+X3+1</f>
         <v>9</v>
       </c>
       <c r="AA3" s="31"/>
       <c r="AB3" s="31">
-        <f>+Z3+1</f>
         <v>10</v>
       </c>
       <c r="AC3" s="31"/>
       <c r="AD3" s="31">
-        <f>+AB3+1</f>
         <v>11</v>
       </c>
       <c r="AE3" s="31"/>
       <c r="AF3" s="31">
-        <f>+AD3+1</f>
         <v>12</v>
       </c>
       <c r="AG3" s="31"/>
       <c r="AH3" s="31">
-        <f>+AF3+1</f>
         <v>13</v>
       </c>
       <c r="AI3" s="31"/>
       <c r="AJ3" s="31">
-        <f>+AH3+1</f>
         <v>14</v>
       </c>
       <c r="AK3" s="31"/>
       <c r="AL3" s="31">
-        <f>+AJ3+1</f>
         <v>15</v>
       </c>
       <c r="AM3" s="31"/>
       <c r="AN3" s="31">
-        <f>+AL3+1</f>
         <v>16</v>
       </c>
       <c r="AO3" s="31"/>
       <c r="AP3" s="31">
-        <f>+AN3+1</f>
         <v>17</v>
       </c>
       <c r="AQ3" s="31"/>
       <c r="AR3" s="31">
-        <f>+AP3+1</f>
         <v>18</v>
       </c>
       <c r="AS3" s="31"/>
       <c r="AT3" s="31">
-        <f>+AR3+1</f>
         <v>19</v>
       </c>
       <c r="AU3" s="31"/>
       <c r="AV3" s="31">
-        <f>+AT3+1</f>
         <v>20</v>
       </c>
       <c r="AW3" s="31"/>
       <c r="AX3" s="31">
-        <f>+AV3+1</f>
         <v>21</v>
       </c>
       <c r="AY3" s="31"/>
       <c r="AZ3" s="31">
-        <f>+AX3+1</f>
         <v>22</v>
       </c>
       <c r="BA3" s="31"/>
       <c r="BB3" s="31">
-        <f>+AZ3+1</f>
         <v>23</v>
       </c>
       <c r="BC3" s="31"/>
       <c r="BD3" s="31">
-        <f>+BB3+1</f>
         <v>24</v>
       </c>
       <c r="BE3" s="31"/>
       <c r="BF3" s="31">
-        <f>+BD3+1</f>
         <v>25</v>
       </c>
       <c r="BG3" s="31"/>
       <c r="BH3" s="31">
-        <f>+BF3+1</f>
         <v>26</v>
       </c>
       <c r="BI3" s="31"/>
       <c r="BJ3" s="31">
-        <f>+BH3+1</f>
         <v>27</v>
       </c>
       <c r="BK3" s="171"/>
       <c r="BL3" s="31">
-        <f>+BJ3+1</f>
         <v>28</v>
       </c>
       <c r="BM3" s="31"/>
       <c r="BN3" s="31">
-        <f>+BL3+1</f>
         <v>29</v>
       </c>
       <c r="BO3" s="31"/>
-      <c r="BP3" s="172">
-        <f>+BN3+1</f>
+      <c r="BP3" s="173">
         <v>30</v>
       </c>
-      <c r="BQ3" s="173"/>
-      <c r="BR3" s="172">
-        <f>+BP3+1</f>
+      <c r="BQ3" s="174"/>
+      <c r="BR3" s="173">
         <v>31</v>
       </c>
-      <c r="BS3" s="173"/>
+      <c r="BS3" s="174"/>
       <c r="CA3" s="148" t="s">
         <v>706</v>
       </c>
@@ -33357,9 +33331,6 @@
   <headerFooter>
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
-  <ignoredErrors>
-    <ignoredError sqref="BR3"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -33461,16 +33432,16 @@
       <c r="F4" s="66"/>
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
-      <c r="I4" s="174" t="s">
+      <c r="I4" s="175" t="s">
         <v>498</v>
       </c>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
-      <c r="L4" s="176"/>
-      <c r="M4" s="174" t="s">
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="177"/>
+      <c r="M4" s="175" t="s">
         <v>499</v>
       </c>
-      <c r="N4" s="176"/>
+      <c r="N4" s="177"/>
       <c r="O4" s="67"/>
       <c r="BU4" s="169"/>
       <c r="BX4" s="169"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_8F3D3109B6CE6C95635AAC206AEC06CC75D307F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC7B831E-E4ED-45C5-A4BC-B11A07C18CA0}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_8F3D3109B6CE6C95635AAC206AEC06CC75D307F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{851448F1-7BA3-4F47-8486-32F9BEE4549F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2718,7 +2718,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:CS167"/>
+  <dimension ref="A1:BL167"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.21875" style="16" bestFit="1" customWidth="1"/>
